--- a/client_gamedata/ios/settings.xlsx
+++ b/client_gamedata/ios/settings.xlsx
@@ -415,7 +415,7 @@
         <v>CONFIG_MEMO</v>
       </c>
       <c r="B2" t="str">
-        <v>prod-4_6_0 (client-4.6.0; server-4.6.0)</v>
+        <v>prod-4_7_0 (client-4.7.0; server-4.6.0)</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         <v>IMPERIUM_DOWNLOAD_DATA_ANDROID_TAG_UUID</v>
       </c>
       <c r="B11" t="str">
-        <v>ESahAX+FGZYZOOboRrs06nbNWhDe2WulS4tIAmx19bgW2O/rHhQvJQuCO/i9uBxd</v>
+        <v>IIDMdqN5aUtdjsQ7GWMY+jNKFezN10p+tlsMXPep5Vp2hhBDn5pRLPR3HhAIWufC</v>
       </c>
     </row>
     <row r="12">
@@ -495,7 +495,7 @@
         <v>IMPERIUM_DOWNLOAD_DATA_IOS_TAG_UUID</v>
       </c>
       <c r="B12" t="str">
-        <v>K5j7FZwG0qrrvbOZGZt6AFL3KYAi7dnXi3SiXm1dJ2ZggcECPiOmMSnMUql5ZLN+</v>
+        <v>5btIDSdCoAx5TBN2eA9++NP1IjMV0JwYRyenVbzKEoVwDCTfM5Omaro1+JDKZyZi</v>
       </c>
     </row>
     <row r="13">
@@ -591,7 +591,7 @@
         <v>IMPERIUM_ANDROID_EXP_TAG_UUID</v>
       </c>
       <c r="B24" t="str">
-        <v>mIWEycOp/pPDdH+hI4crCadpU5li0J0imV7ZRu3HJOuQnC+kgOvD3lRDistYL0eX</v>
+        <v>+q0hxW8mRdUYfkZEz7UdcaCqfTcWX3+unBLBt2a7JAZIzSO0d8/hZmpM0wAyn1+G</v>
       </c>
     </row>
     <row r="25">
@@ -599,7 +599,7 @@
         <v>IMPERIUM_IOS_EXP_TAG_UUID</v>
       </c>
       <c r="B25" t="str">
-        <v>ru1yiAkdrE6ZsueT4nbDgefmUg+xZpcRL/Pj98t+AsCycsdy5X65nBiHQr4NI4VP</v>
+        <v>tH2WNmB9+3E9Qb8iHNgtPhiZkHTMjrTlKlKlwVjL3LiAbUEWSVHyIcbErDWb4ir2</v>
       </c>
     </row>
     <row r="26">
@@ -607,7 +607,7 @@
         <v>IMPERIUM_CHAR_ASSETS_TAG_UUID</v>
       </c>
       <c r="B26" t="str">
-        <v>GBI6/MhQeQTpwrgPnvdAQwFyREwvX0qYolTjj9GRYNzl9YRtitYuVx+/BiTpxbxJ</v>
+        <v>JpoDm/tG6pUlelxvPJiDOXPAS63IDP8FadDhSpd95JsFrNRlfEOW0M5h5pBKr6B5</v>
       </c>
     </row>
     <row r="27">
@@ -615,7 +615,7 @@
         <v>IMPERIUM_DIALOG_TAG_UUID</v>
       </c>
       <c r="B27" t="str">
-        <v>0MyL5r9GzxOxwGIlnwvEFn1IlpLrVcX6gxiTAz1O5tEaCLHQc9llDHwGP7in54HS</v>
+        <v>dmHawfwRSaxs6jpFuC+bNp8ZDTioJnpjW0Gko+0xjVvT8veH0bSB3Q5RDTD/7LIV</v>
       </c>
     </row>
   </sheetData>
